--- a/artfynd/A 4757-2023 artfynd.xlsx
+++ b/artfynd/A 4757-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4757-2023 artfynd.xlsx
+++ b/artfynd/A 4757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112640696</v>
+        <v>112640860</v>
       </c>
       <c r="B2" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428897</v>
+        <v>428904</v>
       </c>
       <c r="R2" t="n">
-        <v>6935078</v>
+        <v>6935248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112640727</v>
+        <v>112640835</v>
       </c>
       <c r="B3" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428684</v>
+        <v>428794</v>
       </c>
       <c r="R3" t="n">
-        <v>6934847</v>
+        <v>6934964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112640724</v>
+        <v>112640838</v>
       </c>
       <c r="B4" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428701</v>
+        <v>428615</v>
       </c>
       <c r="R4" t="n">
-        <v>6934863</v>
+        <v>6934910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112640730</v>
+        <v>112640841</v>
       </c>
       <c r="B5" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428563</v>
+        <v>428560</v>
       </c>
       <c r="R5" t="n">
-        <v>6934901</v>
+        <v>6934803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112640827</v>
+        <v>112640844</v>
       </c>
       <c r="B6" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428695</v>
+        <v>428567</v>
       </c>
       <c r="R6" t="n">
-        <v>6934865</v>
+        <v>6934820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112640682</v>
+        <v>112640848</v>
       </c>
       <c r="B7" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428328</v>
+        <v>428573</v>
       </c>
       <c r="R7" t="n">
-        <v>6934811</v>
+        <v>6934832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112640844</v>
+        <v>112640851</v>
       </c>
       <c r="B8" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1372,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428567</v>
+        <v>428503</v>
       </c>
       <c r="R8" t="n">
-        <v>6934820</v>
+        <v>6934716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112640851</v>
+        <v>112640677</v>
       </c>
       <c r="B9" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1365,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428503</v>
+        <v>428124</v>
       </c>
       <c r="R9" t="n">
-        <v>6934717</v>
+        <v>6934552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,6 +1429,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,15 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112640692</v>
+        <v>112640679</v>
       </c>
       <c r="B10" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428909</v>
+        <v>428129</v>
       </c>
       <c r="R10" t="n">
-        <v>6935246</v>
+        <v>6934566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112640684</v>
+        <v>112640680</v>
       </c>
       <c r="B11" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428482</v>
+        <v>428193</v>
       </c>
       <c r="R11" t="n">
-        <v>6934937</v>
+        <v>6934648</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1645,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,15 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112640687</v>
+        <v>112640681</v>
       </c>
       <c r="B12" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428615</v>
+        <v>428277</v>
       </c>
       <c r="R12" t="n">
-        <v>6934978</v>
+        <v>6934780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1751,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112640732</v>
+        <v>112640682</v>
       </c>
       <c r="B13" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428577</v>
+        <v>428328</v>
       </c>
       <c r="R13" t="n">
-        <v>6934866</v>
+        <v>6934811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,15 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112640823</v>
+        <v>112640684</v>
       </c>
       <c r="B14" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,34 +1895,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428935</v>
+        <v>428481</v>
       </c>
       <c r="R14" t="n">
-        <v>6935116</v>
+        <v>6934937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,6 +1959,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,15 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112640679</v>
+        <v>112640685</v>
       </c>
       <c r="B15" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428129</v>
+        <v>428500</v>
       </c>
       <c r="R15" t="n">
-        <v>6934566</v>
+        <v>6934925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2069,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,15 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112640822</v>
+        <v>112640686</v>
       </c>
       <c r="B16" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2107,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428616</v>
+        <v>428582</v>
       </c>
       <c r="R16" t="n">
-        <v>6934988</v>
+        <v>6934955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,6 +2171,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,15 +2202,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112640825</v>
+        <v>112640687</v>
       </c>
       <c r="B17" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2213,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428827</v>
+        <v>428615</v>
       </c>
       <c r="R17" t="n">
-        <v>6935019</v>
+        <v>6934978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,6 +2277,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,15 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112640685</v>
+        <v>112640688</v>
       </c>
       <c r="B18" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428500</v>
+        <v>428599</v>
       </c>
       <c r="R18" t="n">
-        <v>6934924</v>
+        <v>6934990</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2387,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,15 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112640694</v>
+        <v>112640689</v>
       </c>
       <c r="B19" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428912</v>
+        <v>428693</v>
       </c>
       <c r="R19" t="n">
-        <v>6935277</v>
+        <v>6935070</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2493,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,15 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112640705</v>
+        <v>112640690</v>
       </c>
       <c r="B20" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428787</v>
+        <v>428878</v>
       </c>
       <c r="R20" t="n">
-        <v>6935013</v>
+        <v>6935178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2599,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,15 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112640715</v>
+        <v>112640691</v>
       </c>
       <c r="B21" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428714</v>
+        <v>428895</v>
       </c>
       <c r="R21" t="n">
-        <v>6934961</v>
+        <v>6935234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,15 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112640838</v>
+        <v>112640692</v>
       </c>
       <c r="B22" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,34 +2743,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428615</v>
+        <v>428910</v>
       </c>
       <c r="R22" t="n">
-        <v>6934910</v>
+        <v>6935246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,6 +2807,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,15 +2838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112640848</v>
+        <v>112640693</v>
       </c>
       <c r="B23" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,34 +2849,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428573</v>
+        <v>428906</v>
       </c>
       <c r="R23" t="n">
-        <v>6934832</v>
+        <v>6935244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,6 +2913,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,15 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112640713</v>
+        <v>112640694</v>
       </c>
       <c r="B24" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3089,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428722</v>
+        <v>428912</v>
       </c>
       <c r="R24" t="n">
-        <v>6934979</v>
+        <v>6935276</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3023,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,12 +3053,7 @@
         <v>112640695</v>
       </c>
       <c r="B25" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,15 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112640710</v>
+        <v>112640696</v>
       </c>
       <c r="B26" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428804</v>
+        <v>428898</v>
       </c>
       <c r="R26" t="n">
-        <v>6934939</v>
+        <v>6935078</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,7 +3235,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,15 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112640728</v>
+        <v>112640697</v>
       </c>
       <c r="B27" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3422,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428691</v>
+        <v>428900</v>
       </c>
       <c r="R27" t="n">
-        <v>6934849</v>
+        <v>6935078</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,7 +3341,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,15 +3368,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112640828</v>
+        <v>112640698</v>
       </c>
       <c r="B28" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,34 +3379,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428565</v>
+        <v>428913</v>
       </c>
       <c r="R28" t="n">
-        <v>6934822</v>
+        <v>6935078</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3565,6 +3443,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,15 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112640734</v>
+        <v>112640699</v>
       </c>
       <c r="B29" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3635,10 +3513,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428531</v>
+        <v>428881</v>
       </c>
       <c r="R29" t="n">
-        <v>6934795</v>
+        <v>6935060</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,7 +3553,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3702,15 +3580,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112640677</v>
+        <v>112640700</v>
       </c>
       <c r="B30" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3619,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428125</v>
+        <v>428884</v>
       </c>
       <c r="R30" t="n">
-        <v>6934552</v>
+        <v>6935029</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3659,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,15 +3686,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112640698</v>
+        <v>112640701</v>
       </c>
       <c r="B31" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3857,10 +3725,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428914</v>
+        <v>428880</v>
       </c>
       <c r="R31" t="n">
-        <v>6935078</v>
+        <v>6935026</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3924,15 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112640717</v>
+        <v>112640702</v>
       </c>
       <c r="B32" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428741</v>
+        <v>428878</v>
       </c>
       <c r="R32" t="n">
-        <v>6934935</v>
+        <v>6935023</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4035,15 +3898,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112640697</v>
+        <v>112640703</v>
       </c>
       <c r="B33" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428899</v>
+        <v>428813</v>
       </c>
       <c r="R33" t="n">
-        <v>6935078</v>
+        <v>6935019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4146,15 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112640731</v>
+        <v>112640704</v>
       </c>
       <c r="B34" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4190,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428576</v>
+        <v>428797</v>
       </c>
       <c r="R34" t="n">
-        <v>6934878</v>
+        <v>6935023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4230,7 +4083,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,15 +4110,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112640720</v>
+        <v>112640705</v>
       </c>
       <c r="B35" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4301,10 +4149,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428667</v>
+        <v>428786</v>
       </c>
       <c r="R35" t="n">
-        <v>6934877</v>
+        <v>6935013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4341,7 +4189,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4368,15 +4216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112640835</v>
+        <v>112640707</v>
       </c>
       <c r="B36" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4384,34 +4227,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428794</v>
+        <v>428827</v>
       </c>
       <c r="R36" t="n">
-        <v>6934964</v>
+        <v>6934946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4444,6 +4291,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,15 +4322,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112640725</v>
+        <v>112640708</v>
       </c>
       <c r="B37" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4514,10 +4361,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428695</v>
+        <v>428820</v>
       </c>
       <c r="R37" t="n">
-        <v>6934864</v>
+        <v>6934944</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4401,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4581,15 +4428,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112640726</v>
+        <v>112640709</v>
       </c>
       <c r="B38" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4625,10 +4467,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428693</v>
+        <v>428810</v>
       </c>
       <c r="R38" t="n">
-        <v>6934854</v>
+        <v>6934946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4665,7 +4507,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,15 +4534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112640681</v>
+        <v>112640710</v>
       </c>
       <c r="B39" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4736,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428278</v>
+        <v>428804</v>
       </c>
       <c r="R39" t="n">
-        <v>6934780</v>
+        <v>6934939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4803,15 +4640,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112640716</v>
+        <v>112640712</v>
       </c>
       <c r="B40" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4847,10 +4679,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428731</v>
+        <v>428742</v>
       </c>
       <c r="R40" t="n">
-        <v>6934956</v>
+        <v>6934987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4887,7 +4719,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4914,15 +4746,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112640721</v>
+        <v>112640713</v>
       </c>
       <c r="B41" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,10 +4785,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428679</v>
+        <v>428722</v>
       </c>
       <c r="R41" t="n">
-        <v>6934867</v>
+        <v>6934979</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,15 +4852,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112640707</v>
+        <v>112640715</v>
       </c>
       <c r="B42" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5069,10 +4891,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428827</v>
+        <v>428714</v>
       </c>
       <c r="R42" t="n">
-        <v>6934946</v>
+        <v>6934961</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,7 +4931,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5136,15 +4958,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112640722</v>
+        <v>112640716</v>
       </c>
       <c r="B43" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5180,10 +4997,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428685</v>
+        <v>428731</v>
       </c>
       <c r="R43" t="n">
-        <v>6934865</v>
+        <v>6934956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5247,15 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112640688</v>
+        <v>112640717</v>
       </c>
       <c r="B44" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5291,10 +5103,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428599</v>
+        <v>428741</v>
       </c>
       <c r="R44" t="n">
-        <v>6934991</v>
+        <v>6934936</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5331,7 +5143,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5358,15 +5170,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112640719</v>
+        <v>112640718</v>
       </c>
       <c r="B45" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,10 +5209,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428665</v>
+        <v>428651</v>
       </c>
       <c r="R45" t="n">
-        <v>6934878</v>
+        <v>6934880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5442,7 +5249,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5469,15 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112640703</v>
+        <v>112640719</v>
       </c>
       <c r="B46" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5513,10 +5315,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428813</v>
+        <v>428665</v>
       </c>
       <c r="R46" t="n">
-        <v>6935019</v>
+        <v>6934879</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5580,15 +5382,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112640699</v>
+        <v>112640720</v>
       </c>
       <c r="B47" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5624,10 +5421,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428881</v>
+        <v>428667</v>
       </c>
       <c r="R47" t="n">
-        <v>6935060</v>
+        <v>6934878</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5664,7 +5461,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5691,15 +5488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112640826</v>
+        <v>112640721</v>
       </c>
       <c r="B48" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5707,34 +5499,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428736</v>
+        <v>428679</v>
       </c>
       <c r="R48" t="n">
-        <v>6934983</v>
+        <v>6934868</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5767,6 +5563,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5793,50 +5594,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112640860</v>
+        <v>112640722</v>
       </c>
       <c r="B49" t="n">
-        <v>90458</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428903</v>
+        <v>428686</v>
       </c>
       <c r="R49" t="n">
-        <v>6935248</v>
+        <v>6934865</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5869,6 +5669,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5895,15 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112640718</v>
+        <v>112640723</v>
       </c>
       <c r="B50" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5939,10 +5739,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428651</v>
+        <v>428705</v>
       </c>
       <c r="R50" t="n">
-        <v>6934880</v>
+        <v>6934858</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5979,7 +5779,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6006,15 +5806,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112640700</v>
+        <v>112640724</v>
       </c>
       <c r="B51" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6050,10 +5845,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428884</v>
+        <v>428700</v>
       </c>
       <c r="R51" t="n">
-        <v>6935029</v>
+        <v>6934863</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6090,7 +5885,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6117,15 +5912,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112640701</v>
+        <v>112640725</v>
       </c>
       <c r="B52" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,10 +5951,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428880</v>
+        <v>428694</v>
       </c>
       <c r="R52" t="n">
-        <v>6935026</v>
+        <v>6934864</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6228,15 +6018,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112640693</v>
+        <v>112640726</v>
       </c>
       <c r="B53" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6272,10 +6057,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428907</v>
+        <v>428693</v>
       </c>
       <c r="R53" t="n">
-        <v>6935244</v>
+        <v>6934854</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6339,15 +6124,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112640704</v>
+        <v>112640727</v>
       </c>
       <c r="B54" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6383,10 +6163,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428797</v>
+        <v>428683</v>
       </c>
       <c r="R54" t="n">
-        <v>6935023</v>
+        <v>6934848</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6423,7 +6203,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6450,15 +6230,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112640691</v>
+        <v>112640728</v>
       </c>
       <c r="B55" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6494,10 +6269,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428895</v>
+        <v>428691</v>
       </c>
       <c r="R55" t="n">
-        <v>6935234</v>
+        <v>6934849</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6309,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6564,12 +6339,7 @@
         <v>112640729</v>
       </c>
       <c r="B56" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6608,7 +6378,7 @@
         <v>428582</v>
       </c>
       <c r="R56" t="n">
-        <v>6934835</v>
+        <v>6934836</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6672,15 +6442,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112640709</v>
+        <v>112640730</v>
       </c>
       <c r="B57" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6716,10 +6481,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428810</v>
+        <v>428563</v>
       </c>
       <c r="R57" t="n">
-        <v>6934946</v>
+        <v>6934901</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6783,15 +6548,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112640841</v>
+        <v>112640731</v>
       </c>
       <c r="B58" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6799,34 +6559,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428560</v>
+        <v>428576</v>
       </c>
       <c r="R58" t="n">
-        <v>6934803</v>
+        <v>6934878</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6859,6 +6623,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6885,15 +6654,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112640735</v>
+        <v>112640732</v>
       </c>
       <c r="B59" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6929,10 +6693,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428532</v>
+        <v>428577</v>
       </c>
       <c r="R59" t="n">
-        <v>6934750</v>
+        <v>6934866</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6969,7 +6733,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6996,15 +6760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112640832</v>
+        <v>112640733</v>
       </c>
       <c r="B60" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7012,34 +6771,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>stornäshållan sör-vemhån, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428550</v>
+        <v>428461</v>
       </c>
       <c r="R60" t="n">
-        <v>6934885</v>
+        <v>6934829</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7072,6 +6835,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7098,15 +6866,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112640723</v>
+        <v>112640734</v>
       </c>
       <c r="B61" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,10 +6905,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428706</v>
+        <v>428531</v>
       </c>
       <c r="R61" t="n">
-        <v>6934858</v>
+        <v>6934795</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7209,15 +6972,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112640686</v>
+        <v>112640735</v>
       </c>
       <c r="B62" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7253,10 +7011,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428582</v>
+        <v>428532</v>
       </c>
       <c r="R62" t="n">
-        <v>6934955</v>
+        <v>6934750</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7320,15 +7078,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112640702</v>
+        <v>112640736</v>
       </c>
       <c r="B63" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7364,10 +7117,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428878</v>
+        <v>428502</v>
       </c>
       <c r="R63" t="n">
-        <v>6935023</v>
+        <v>6934704</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7431,15 +7184,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112640690</v>
+        <v>112640737</v>
       </c>
       <c r="B64" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7475,10 +7223,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428878</v>
+        <v>428159</v>
       </c>
       <c r="R64" t="n">
-        <v>6935178</v>
+        <v>6934561</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7539,561 +7287,6 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>112640708</v>
-      </c>
-      <c r="B65" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>stornäshållan sör-vemhån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>428820</v>
-      </c>
-      <c r="R65" t="n">
-        <v>6934943</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>112640733</v>
-      </c>
-      <c r="B66" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>stornäshållan sör-vemhån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>428461</v>
-      </c>
-      <c r="R66" t="n">
-        <v>6934829</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>112640737</v>
-      </c>
-      <c r="B67" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>stornäshållan sör-vemhån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>428160</v>
-      </c>
-      <c r="R67" t="n">
-        <v>6934561</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>112640689</v>
-      </c>
-      <c r="B68" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>stornäshållan sör-vemhån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>428693</v>
-      </c>
-      <c r="R68" t="n">
-        <v>6935070</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>112640712</v>
-      </c>
-      <c r="B69" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>stornäshållan sör-vemhån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>428742</v>
-      </c>
-      <c r="R69" t="n">
-        <v>6934987</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4757-2023 artfynd.xlsx
+++ b/artfynd/A 4757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640860</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640838</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640848</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640851</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640677</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640679</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640680</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640681</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640682</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640685</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2199,6 +2274,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640686</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640687</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640688</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640689</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640690</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640691</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640692</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640693</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640694</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3153,6 +3273,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640695</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640696</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,6 +3495,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640697</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3471,6 +3606,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640698</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3577,6 +3717,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640699</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640700</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3789,6 +3939,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640701</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3895,6 +4050,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640702</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4001,6 +4161,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640703</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4107,6 +4272,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640704</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4213,6 +4383,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640705</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4319,6 +4494,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640707</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4425,6 +4605,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640708</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4531,6 +4716,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640709</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4637,6 +4827,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640710</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4743,6 +4938,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640712</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4849,6 +5049,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640713</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4955,6 +5160,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640715</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5061,6 +5271,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640716</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5167,6 +5382,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640717</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5273,6 +5493,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640718</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5379,6 +5604,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640719</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5485,6 +5715,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640720</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5591,6 +5826,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640721</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5697,6 +5937,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640722</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5803,6 +6048,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640723</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5909,6 +6159,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640724</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6015,6 +6270,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640725</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6121,6 +6381,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640726</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6227,6 +6492,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640727</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6333,6 +6603,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640728</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6439,6 +6714,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640729</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6545,6 +6825,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640730</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6651,6 +6936,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640731</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6757,6 +7047,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640732</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6863,6 +7158,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640733</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6969,6 +7269,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640734</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7075,6 +7380,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640735</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7181,6 +7491,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640736</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7287,8 +7602,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112640737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>